--- a/CodeSystem-assistance-needs-cs.xlsx
+++ b/CodeSystem-assistance-needs-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://ig.opennz.org/CodeSystem/assistance-needs-cs</t>
+    <t>https://ig.opennz.org/CodeSystem/assistance-needs-cs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T09:45:49+00:00</t>
+    <t>2024-06-13T01:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>FHIR New Republic (http://ig.opennz.org)</t>
+    <t>FHIR New Republic (https://ig.opennz.org)</t>
   </si>
   <si>
     <t>Description</t>

--- a/CodeSystem-assistance-needs-cs.xlsx
+++ b/CodeSystem-assistance-needs-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-13T01:01:15+00:00</t>
+    <t>2024-06-13T05:29:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-assistance-needs-cs.xlsx
+++ b/CodeSystem-assistance-needs-cs.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AssistanceNeedsCodeSet</t>
+    <t>AssistanceNeedsCodeSystem</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-13T05:29:47+00:00</t>
+    <t>2024-06-21T01:45:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -135,13 +135,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>nzsli</t>
+    <t>171671000210109</t>
   </si>
   <si>
     <t>A New Zealand Sign Language interpreter</t>
   </si>
   <si>
-    <t>smd</t>
+    <t>133920001</t>
   </si>
   <si>
     <t>Support to make decisions</t>

--- a/CodeSystem-assistance-needs-cs.xlsx
+++ b/CodeSystem-assistance-needs-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T01:45:26+00:00</t>
+    <t>2024-06-21T04:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
